--- a/bio_workcell/active_runs/Sample Excel Experiment Run Document.xlsx
+++ b/bio_workcell/active_runs/Sample Excel Experiment Run Document.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ademi\Documents\Career\Internships\Argonne SULI - Summer 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ademi\Documents\Career\Internships\Argonne SULI - Summer 2023\BIO_workcell\bio_workcell\active_runs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3249DC7-2EF6-433E-83E0-EBF5A159A307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A46A4D0-41E9-4165-8EB9-293DF8CF962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{BC1A8ACE-1376-4C95-9AFE-E5DEC12F6A8A}"/>
   </bookViews>
@@ -29,7 +29,6 @@
     <sheet name="Run 12" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Run Number</t>
   </si>
@@ -71,6 +70,9 @@
   </si>
   <si>
     <t>Possible Run Matrix</t>
+  </si>
+  <si>
+    <t>Incubation Time (Hours)</t>
   </si>
 </sst>
 </file>
@@ -444,6 +446,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.45">
@@ -451,6 +454,12 @@
         <v>3</v>
       </c>
       <c r="B1">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1">
         <v>1</v>
       </c>
     </row>
@@ -462,25 +471,25 @@
         <f>IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="str">
+      <c r="C3" s="1">
         <f t="shared" ref="C3:M3" si="0">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
-        <v/>
-      </c>
-      <c r="D3" s="1" t="str">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="1" t="str">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F3" s="1" t="str">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="str">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -511,12 +520,24 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>6</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -529,12 +550,24 @@
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7</v>
+      </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -4756,23 +4789,23 @@
       </c>
       <c r="B8" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="C8" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="D8" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="E8" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="F8" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="G8" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
@@ -7566,23 +7599,23 @@
       </c>
       <c r="B9" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="C9" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="D9" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="E9" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="F9" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="G9" t="str">
         <f>IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
@@ -10383,813 +10416,813 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="str">
+      <c r="A2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C2" t="str">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E2" t="str">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F2" t="str">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G2" t="str">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H2" t="str">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I2" t="str">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L2" t="str">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="str">
+      <c r="A3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B3" t="str">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C3" t="str">
+        <v>1</v>
+      </c>
+      <c r="C3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D3" t="str">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G3" t="str">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H3" t="str">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I3" t="str">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L3" t="str">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
+      <c r="A4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B4" t="str">
+        <v>1</v>
+      </c>
+      <c r="B4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C4" t="str">
+        <v>1</v>
+      </c>
+      <c r="C4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D4" t="str">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E4" t="str">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F4" t="str">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G4" t="str">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H4" t="str">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I4" t="str">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L4" t="str">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B5" t="str">
+        <v>1</v>
+      </c>
+      <c r="B5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C5" t="str">
+        <v>1</v>
+      </c>
+      <c r="C5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D5" t="str">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E5" t="str">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F5" t="str">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G5" t="str">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H5" t="str">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I5" t="str">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L5" t="str">
+        <v>1</v>
+      </c>
+      <c r="L5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B6" t="str">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C6" t="str">
+        <v>1</v>
+      </c>
+      <c r="C6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D6" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E6" t="str">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F6" t="str">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G6" t="str">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H6" t="str">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I6" t="str">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L6" t="str">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
+      <c r="A7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>1</v>
+      </c>
+      <c r="L7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
+      <c r="A8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B8" t="str">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C8" t="str">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D8" t="str">
+        <v>1</v>
+      </c>
+      <c r="D8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E8" t="str">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G8" t="str">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H8" t="str">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L8" t="str">
+        <v>1</v>
+      </c>
+      <c r="L8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="str">
+      <c r="A9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="C9" t="str">
+        <v>1</v>
+      </c>
+      <c r="C9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D9" t="str">
+        <v>1</v>
+      </c>
+      <c r="D9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="G9" t="str">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="H9" t="str">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="K9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L9" t="str">
+        <v>1</v>
+      </c>
+      <c r="L9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$4)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="str">
+      <c r="A12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B12" t="str">
+        <v>2</v>
+      </c>
+      <c r="B12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C12" t="str">
+        <v>2</v>
+      </c>
+      <c r="C12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D12" t="str">
+        <v>2</v>
+      </c>
+      <c r="D12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="E12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G12" t="str">
+        <v>2</v>
+      </c>
+      <c r="G12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H12" t="str">
+        <v>2</v>
+      </c>
+      <c r="H12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>2</v>
+      </c>
+      <c r="I12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J12" t="str">
+        <v>2</v>
+      </c>
+      <c r="J12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K12" t="str">
+        <v>2</v>
+      </c>
+      <c r="K12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L12" t="str">
+        <v>2</v>
+      </c>
+      <c r="L12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="str">
+      <c r="A13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B13" t="str">
+        <v>2</v>
+      </c>
+      <c r="B13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C13" t="str">
+        <v>2</v>
+      </c>
+      <c r="C13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D13" t="str">
+        <v>2</v>
+      </c>
+      <c r="D13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E13" t="str">
+        <v>2</v>
+      </c>
+      <c r="E13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+        <v>2</v>
+      </c>
+      <c r="F13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v>2</v>
+      </c>
+      <c r="G13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H13" t="str">
+        <v>2</v>
+      </c>
+      <c r="H13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>2</v>
+      </c>
+      <c r="I13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J13" t="str">
+        <v>2</v>
+      </c>
+      <c r="J13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K13" t="str">
+        <v>2</v>
+      </c>
+      <c r="K13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L13" t="str">
+        <v>2</v>
+      </c>
+      <c r="L13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="str">
+      <c r="A14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B14" t="str">
+        <v>2</v>
+      </c>
+      <c r="B14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C14" t="str">
+        <v>2</v>
+      </c>
+      <c r="C14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D14" t="str">
+        <v>2</v>
+      </c>
+      <c r="D14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E14" t="str">
+        <v>2</v>
+      </c>
+      <c r="E14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+        <v>2</v>
+      </c>
+      <c r="F14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G14" t="str">
+        <v>2</v>
+      </c>
+      <c r="G14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H14" t="str">
+        <v>2</v>
+      </c>
+      <c r="H14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>2</v>
+      </c>
+      <c r="I14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J14" t="str">
+        <v>2</v>
+      </c>
+      <c r="J14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K14" t="str">
+        <v>2</v>
+      </c>
+      <c r="K14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L14" t="str">
+        <v>2</v>
+      </c>
+      <c r="L14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>2</v>
+      </c>
+      <c r="B15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C15" t="str">
+        <v>2</v>
+      </c>
+      <c r="C15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D15" t="str">
+        <v>2</v>
+      </c>
+      <c r="D15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
+        <v>2</v>
+      </c>
+      <c r="E15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+        <v>2</v>
+      </c>
+      <c r="F15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
+        <v>2</v>
+      </c>
+      <c r="G15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H15" t="str">
+        <v>2</v>
+      </c>
+      <c r="H15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I15" t="str">
+        <v>2</v>
+      </c>
+      <c r="I15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J15" t="str">
+        <v>2</v>
+      </c>
+      <c r="J15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K15" t="str">
+        <v>2</v>
+      </c>
+      <c r="K15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L15" t="str">
+        <v>2</v>
+      </c>
+      <c r="L15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="str">
+      <c r="A16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B16" t="str">
+        <v>2</v>
+      </c>
+      <c r="B16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C16" t="str">
+        <v>2</v>
+      </c>
+      <c r="C16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D16" t="str">
+        <v>2</v>
+      </c>
+      <c r="D16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
+        <v>2</v>
+      </c>
+      <c r="E16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>2</v>
+      </c>
+      <c r="G16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H16" t="str">
+        <v>2</v>
+      </c>
+      <c r="H16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v>2</v>
+      </c>
+      <c r="I16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J16" t="str">
+        <v>2</v>
+      </c>
+      <c r="J16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K16" t="str">
+        <v>2</v>
+      </c>
+      <c r="K16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L16" t="str">
+        <v>2</v>
+      </c>
+      <c r="L16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="str">
+      <c r="A17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B17" t="str">
+        <v>2</v>
+      </c>
+      <c r="B17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C17" t="str">
+        <v>2</v>
+      </c>
+      <c r="C17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D17" t="str">
+        <v>2</v>
+      </c>
+      <c r="D17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>2</v>
+      </c>
+      <c r="E17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+        <v>2</v>
+      </c>
+      <c r="F17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
+        <v>2</v>
+      </c>
+      <c r="G17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H17" t="str">
+        <v>2</v>
+      </c>
+      <c r="H17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I17" t="str">
+        <v>2</v>
+      </c>
+      <c r="I17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J17" t="str">
+        <v>2</v>
+      </c>
+      <c r="J17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K17" t="str">
+        <v>2</v>
+      </c>
+      <c r="K17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L17" t="str">
+        <v>2</v>
+      </c>
+      <c r="L17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="str">
+      <c r="A18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B18" t="str">
+        <v>2</v>
+      </c>
+      <c r="B18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C18" t="str">
+        <v>2</v>
+      </c>
+      <c r="C18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
+        <v>2</v>
+      </c>
+      <c r="D18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>2</v>
+      </c>
+      <c r="E18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
+        <v>2</v>
+      </c>
+      <c r="G18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H18" t="str">
+        <v>2</v>
+      </c>
+      <c r="H18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I18" t="str">
+        <v>2</v>
+      </c>
+      <c r="I18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J18" t="str">
+        <v>2</v>
+      </c>
+      <c r="J18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K18" t="str">
+        <v>2</v>
+      </c>
+      <c r="K18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L18" t="str">
+        <v>2</v>
+      </c>
+      <c r="L18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="str">
+      <c r="A19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="B19" t="str">
+        <v>2</v>
+      </c>
+      <c r="B19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C19" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D19" t="str">
+        <v>2</v>
+      </c>
+      <c r="D19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
+        <v>2</v>
+      </c>
+      <c r="E19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
+        <v>2</v>
+      </c>
+      <c r="G19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H19" t="str">
+        <v>2</v>
+      </c>
+      <c r="H19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I19" t="str">
+        <v>2</v>
+      </c>
+      <c r="I19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="J19" t="str">
+        <v>2</v>
+      </c>
+      <c r="J19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K19" t="str">
+        <v>2</v>
+      </c>
+      <c r="K19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L19" t="str">
+        <v>2</v>
+      </c>
+      <c r="L19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$B$4),ISBLANK(Complete_Run_Layout!$B$5),ISBLANK(Complete_Run_Layout!$B$3), Complete_Run_Layout!$B$3 = ""), "", Complete_Run_Layout!$B$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -11205,813 +11238,813 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="str">
+      <c r="A2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B2" t="str">
+        <v>2</v>
+      </c>
+      <c r="B2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C2" t="str">
+        <v>2</v>
+      </c>
+      <c r="C2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D2" t="str">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F2" t="str">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G2" t="str">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H2" t="str">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I2" t="str">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J2" t="str">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K2" t="str">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L2" t="str">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="str">
+      <c r="A3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C3" t="str">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D3" t="str">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E3" t="str">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F3" t="str">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G3" t="str">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H3" t="str">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I3" t="str">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J3" t="str">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K3" t="str">
+        <v>2</v>
+      </c>
+      <c r="K3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L3" t="str">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
+      <c r="A4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B4" t="str">
+        <v>2</v>
+      </c>
+      <c r="B4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C4" t="str">
+        <v>2</v>
+      </c>
+      <c r="C4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D4" t="str">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E4" t="str">
+        <v>2</v>
+      </c>
+      <c r="E4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F4" t="str">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G4" t="str">
+        <v>2</v>
+      </c>
+      <c r="G4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H4" t="str">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I4" t="str">
+        <v>2</v>
+      </c>
+      <c r="I4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J4" t="str">
+        <v>2</v>
+      </c>
+      <c r="J4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K4" t="str">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L4" t="str">
+        <v>2</v>
+      </c>
+      <c r="L4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B5" t="str">
+        <v>2</v>
+      </c>
+      <c r="B5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C5" t="str">
+        <v>2</v>
+      </c>
+      <c r="C5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D5" t="str">
+        <v>2</v>
+      </c>
+      <c r="D5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E5" t="str">
+        <v>2</v>
+      </c>
+      <c r="E5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F5" t="str">
+        <v>2</v>
+      </c>
+      <c r="F5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G5" t="str">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H5" t="str">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I5" t="str">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J5" t="str">
+        <v>2</v>
+      </c>
+      <c r="J5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K5" t="str">
+        <v>2</v>
+      </c>
+      <c r="K5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B6" t="str">
+        <v>2</v>
+      </c>
+      <c r="B6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C6" t="str">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D6" t="str">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E6" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F6" t="str">
+        <v>2</v>
+      </c>
+      <c r="F6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G6" t="str">
+        <v>2</v>
+      </c>
+      <c r="G6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H6" t="str">
+        <v>2</v>
+      </c>
+      <c r="H6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I6" t="str">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J6" t="str">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K6" t="str">
+        <v>2</v>
+      </c>
+      <c r="K6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L6" t="str">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
+      <c r="A7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>2</v>
+      </c>
+      <c r="B7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>2</v>
+      </c>
+      <c r="C7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>2</v>
+      </c>
+      <c r="D7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>2</v>
+      </c>
+      <c r="E7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>2</v>
+      </c>
+      <c r="F7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>2</v>
+      </c>
+      <c r="G7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>2</v>
+      </c>
+      <c r="H7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>2</v>
+      </c>
+      <c r="L7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
+      <c r="A8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="B8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+      <c r="D8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E8" t="str">
+        <v>2</v>
+      </c>
+      <c r="E8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G8" t="str">
+        <v>2</v>
+      </c>
+      <c r="G8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H8" t="str">
+        <v>2</v>
+      </c>
+      <c r="H8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>2</v>
+      </c>
+      <c r="I8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J8" t="str">
+        <v>2</v>
+      </c>
+      <c r="J8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K8" t="str">
+        <v>2</v>
+      </c>
+      <c r="K8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L8" t="str">
+        <v>2</v>
+      </c>
+      <c r="L8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="str">
+      <c r="A9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
+        <v>2</v>
+      </c>
+      <c r="B9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C9" t="str">
+        <v>2</v>
+      </c>
+      <c r="C9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D9" t="str">
+        <v>2</v>
+      </c>
+      <c r="D9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>2</v>
+      </c>
+      <c r="E9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+        <v>2</v>
+      </c>
+      <c r="F9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G9" t="str">
+        <v>2</v>
+      </c>
+      <c r="G9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H9" t="str">
+        <v>2</v>
+      </c>
+      <c r="H9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>2</v>
+      </c>
+      <c r="I9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J9" t="str">
+        <v>2</v>
+      </c>
+      <c r="J9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K9" t="str">
+        <v>2</v>
+      </c>
+      <c r="K9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L9" t="str">
+        <v>2</v>
+      </c>
+      <c r="L9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="str">
+      <c r="A12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B12" t="str">
+        <v>3</v>
+      </c>
+      <c r="B12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D12" t="str">
+        <v>3</v>
+      </c>
+      <c r="D12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E12" t="str">
+        <v>3</v>
+      </c>
+      <c r="E12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+        <v>3</v>
+      </c>
+      <c r="F12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G12" t="str">
+        <v>3</v>
+      </c>
+      <c r="G12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H12" t="str">
+        <v>3</v>
+      </c>
+      <c r="H12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>3</v>
+      </c>
+      <c r="I12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J12" t="str">
+        <v>3</v>
+      </c>
+      <c r="J12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K12" t="str">
+        <v>3</v>
+      </c>
+      <c r="K12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L12" t="str">
+        <v>3</v>
+      </c>
+      <c r="L12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="str">
+      <c r="A13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B13" t="str">
+        <v>3</v>
+      </c>
+      <c r="B13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D13" t="str">
+        <v>3</v>
+      </c>
+      <c r="D13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E13" t="str">
+        <v>3</v>
+      </c>
+      <c r="E13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+        <v>3</v>
+      </c>
+      <c r="F13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v>3</v>
+      </c>
+      <c r="G13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H13" t="str">
+        <v>3</v>
+      </c>
+      <c r="H13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>3</v>
+      </c>
+      <c r="I13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J13" t="str">
+        <v>3</v>
+      </c>
+      <c r="J13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K13" t="str">
+        <v>3</v>
+      </c>
+      <c r="K13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L13" t="str">
+        <v>3</v>
+      </c>
+      <c r="L13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="str">
+      <c r="A14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B14" t="str">
+        <v>3</v>
+      </c>
+      <c r="B14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D14" t="str">
+        <v>3</v>
+      </c>
+      <c r="D14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E14" t="str">
+        <v>3</v>
+      </c>
+      <c r="E14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+        <v>3</v>
+      </c>
+      <c r="F14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G14" t="str">
+        <v>3</v>
+      </c>
+      <c r="G14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H14" t="str">
+        <v>3</v>
+      </c>
+      <c r="H14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J14" t="str">
+        <v>3</v>
+      </c>
+      <c r="J14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K14" t="str">
+        <v>3</v>
+      </c>
+      <c r="K14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L14" t="str">
+        <v>3</v>
+      </c>
+      <c r="L14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>3</v>
+      </c>
+      <c r="B15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C15" t="str">
+        <v>3</v>
+      </c>
+      <c r="C15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D15" t="str">
+        <v>3</v>
+      </c>
+      <c r="D15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
+        <v>3</v>
+      </c>
+      <c r="E15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+        <v>3</v>
+      </c>
+      <c r="F15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
+        <v>3</v>
+      </c>
+      <c r="G15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H15" t="str">
+        <v>3</v>
+      </c>
+      <c r="H15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I15" t="str">
+        <v>3</v>
+      </c>
+      <c r="I15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J15" t="str">
+        <v>3</v>
+      </c>
+      <c r="J15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K15" t="str">
+        <v>3</v>
+      </c>
+      <c r="K15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L15" t="str">
+        <v>3</v>
+      </c>
+      <c r="L15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="str">
+      <c r="A16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B16" t="str">
+        <v>3</v>
+      </c>
+      <c r="B16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D16" t="str">
+        <v>3</v>
+      </c>
+      <c r="D16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
+        <v>3</v>
+      </c>
+      <c r="E16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+        <v>3</v>
+      </c>
+      <c r="F16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>3</v>
+      </c>
+      <c r="G16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H16" t="str">
+        <v>3</v>
+      </c>
+      <c r="H16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v>3</v>
+      </c>
+      <c r="I16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J16" t="str">
+        <v>3</v>
+      </c>
+      <c r="J16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K16" t="str">
+        <v>3</v>
+      </c>
+      <c r="K16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L16" t="str">
+        <v>3</v>
+      </c>
+      <c r="L16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="str">
+      <c r="A17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B17" t="str">
+        <v>3</v>
+      </c>
+      <c r="B17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C17" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D17" t="str">
+        <v>3</v>
+      </c>
+      <c r="D17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>3</v>
+      </c>
+      <c r="E17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+        <v>3</v>
+      </c>
+      <c r="F17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
+        <v>3</v>
+      </c>
+      <c r="G17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H17" t="str">
+        <v>3</v>
+      </c>
+      <c r="H17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I17" t="str">
+        <v>3</v>
+      </c>
+      <c r="I17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J17" t="str">
+        <v>3</v>
+      </c>
+      <c r="J17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K17" t="str">
+        <v>3</v>
+      </c>
+      <c r="K17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L17" t="str">
+        <v>3</v>
+      </c>
+      <c r="L17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="str">
+      <c r="A18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B18" t="str">
+        <v>3</v>
+      </c>
+      <c r="B18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C18" t="str">
+        <v>3</v>
+      </c>
+      <c r="C18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
+        <v>3</v>
+      </c>
+      <c r="D18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>3</v>
+      </c>
+      <c r="E18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+        <v>3</v>
+      </c>
+      <c r="F18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
+        <v>3</v>
+      </c>
+      <c r="G18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H18" t="str">
+        <v>3</v>
+      </c>
+      <c r="H18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I18" t="str">
+        <v>3</v>
+      </c>
+      <c r="I18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J18" t="str">
+        <v>3</v>
+      </c>
+      <c r="J18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K18" t="str">
+        <v>3</v>
+      </c>
+      <c r="K18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L18" t="str">
+        <v>3</v>
+      </c>
+      <c r="L18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="str">
+      <c r="A19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B19" t="str">
+        <v>3</v>
+      </c>
+      <c r="B19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C19" t="str">
+        <v>3</v>
+      </c>
+      <c r="C19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D19" t="str">
+        <v>3</v>
+      </c>
+      <c r="D19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
+        <v>3</v>
+      </c>
+      <c r="E19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+        <v>3</v>
+      </c>
+      <c r="F19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
+        <v>3</v>
+      </c>
+      <c r="G19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H19" t="str">
+        <v>3</v>
+      </c>
+      <c r="H19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I19" t="str">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J19" t="str">
+        <v>3</v>
+      </c>
+      <c r="J19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K19" t="str">
+        <v>3</v>
+      </c>
+      <c r="K19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L19" t="str">
+        <v>3</v>
+      </c>
+      <c r="L19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12027,813 +12060,813 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="str">
+      <c r="A2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B2" t="str">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C2" t="str">
+        <v>3</v>
+      </c>
+      <c r="C2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D2" t="str">
+        <v>3</v>
+      </c>
+      <c r="D2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E2" t="str">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G2" t="str">
+        <v>3</v>
+      </c>
+      <c r="G2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H2" t="str">
+        <v>3</v>
+      </c>
+      <c r="H2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I2" t="str">
+        <v>3</v>
+      </c>
+      <c r="I2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J2" t="str">
+        <v>3</v>
+      </c>
+      <c r="J2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K2" t="str">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L2" t="str">
+        <v>3</v>
+      </c>
+      <c r="L2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="str">
+      <c r="A3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B3" t="str">
+        <v>3</v>
+      </c>
+      <c r="B3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C3" t="str">
+        <v>3</v>
+      </c>
+      <c r="C3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D3" t="str">
+        <v>3</v>
+      </c>
+      <c r="D3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E3" t="str">
+        <v>3</v>
+      </c>
+      <c r="E3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F3" t="str">
+        <v>3</v>
+      </c>
+      <c r="F3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G3" t="str">
+        <v>3</v>
+      </c>
+      <c r="G3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H3" t="str">
+        <v>3</v>
+      </c>
+      <c r="H3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I3" t="str">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J3" t="str">
+        <v>3</v>
+      </c>
+      <c r="J3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K3" t="str">
+        <v>3</v>
+      </c>
+      <c r="K3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L3" t="str">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
+      <c r="A4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C4" t="str">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D4" t="str">
+        <v>3</v>
+      </c>
+      <c r="D4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E4" t="str">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F4" t="str">
+        <v>3</v>
+      </c>
+      <c r="F4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G4" t="str">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H4" t="str">
+        <v>3</v>
+      </c>
+      <c r="H4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I4" t="str">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J4" t="str">
+        <v>3</v>
+      </c>
+      <c r="J4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K4" t="str">
+        <v>3</v>
+      </c>
+      <c r="K4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L4" t="str">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B5" t="str">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C5" t="str">
+        <v>3</v>
+      </c>
+      <c r="C5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D5" t="str">
+        <v>3</v>
+      </c>
+      <c r="D5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E5" t="str">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F5" t="str">
+        <v>3</v>
+      </c>
+      <c r="F5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G5" t="str">
+        <v>3</v>
+      </c>
+      <c r="G5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H5" t="str">
+        <v>3</v>
+      </c>
+      <c r="H5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I5" t="str">
+        <v>3</v>
+      </c>
+      <c r="I5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J5" t="str">
+        <v>3</v>
+      </c>
+      <c r="J5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K5" t="str">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L5" t="str">
+        <v>3</v>
+      </c>
+      <c r="L5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B6" t="str">
+        <v>3</v>
+      </c>
+      <c r="B6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C6" t="str">
+        <v>3</v>
+      </c>
+      <c r="C6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D6" t="str">
+        <v>3</v>
+      </c>
+      <c r="D6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E6" t="str">
+        <v>3</v>
+      </c>
+      <c r="E6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F6" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G6" t="str">
+        <v>3</v>
+      </c>
+      <c r="G6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H6" t="str">
+        <v>3</v>
+      </c>
+      <c r="H6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I6" t="str">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J6" t="str">
+        <v>3</v>
+      </c>
+      <c r="J6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K6" t="str">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L6" t="str">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
+      <c r="A7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>3</v>
+      </c>
+      <c r="B7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>3</v>
+      </c>
+      <c r="C7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>3</v>
+      </c>
+      <c r="D7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>3</v>
+      </c>
+      <c r="E7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>3</v>
+      </c>
+      <c r="F7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>3</v>
+      </c>
+      <c r="G7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>3</v>
+      </c>
+      <c r="H7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>3</v>
+      </c>
+      <c r="I7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>3</v>
+      </c>
+      <c r="J7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>3</v>
+      </c>
+      <c r="L7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
+      <c r="A8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B8" t="str">
+        <v>3</v>
+      </c>
+      <c r="B8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C8" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D8" t="str">
+        <v>3</v>
+      </c>
+      <c r="D8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E8" t="str">
+        <v>3</v>
+      </c>
+      <c r="E8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+        <v>3</v>
+      </c>
+      <c r="F8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G8" t="str">
+        <v>3</v>
+      </c>
+      <c r="G8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H8" t="str">
+        <v>3</v>
+      </c>
+      <c r="H8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J8" t="str">
+        <v>3</v>
+      </c>
+      <c r="J8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K8" t="str">
+        <v>3</v>
+      </c>
+      <c r="K8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L8" t="str">
+        <v>3</v>
+      </c>
+      <c r="L8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="str">
+      <c r="A9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="B9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+      <c r="D9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>3</v>
+      </c>
+      <c r="E9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+        <v>3</v>
+      </c>
+      <c r="F9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G9" t="str">
+        <v>3</v>
+      </c>
+      <c r="G9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H9" t="str">
+        <v>3</v>
+      </c>
+      <c r="H9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>3</v>
+      </c>
+      <c r="I9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J9" t="str">
+        <v>3</v>
+      </c>
+      <c r="J9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K9" t="str">
+        <v>3</v>
+      </c>
+      <c r="K9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L9" t="str">
+        <v>3</v>
+      </c>
+      <c r="L9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="str">
+      <c r="A12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B12" t="str">
+        <v>4</v>
+      </c>
+      <c r="B12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C12" t="str">
+        <v>4</v>
+      </c>
+      <c r="C12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D12" t="str">
+        <v>4</v>
+      </c>
+      <c r="D12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E12" t="str">
+        <v>4</v>
+      </c>
+      <c r="E12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+        <v>4</v>
+      </c>
+      <c r="F12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G12" t="str">
+        <v>4</v>
+      </c>
+      <c r="G12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H12" t="str">
+        <v>4</v>
+      </c>
+      <c r="H12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>4</v>
+      </c>
+      <c r="I12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J12" t="str">
+        <v>4</v>
+      </c>
+      <c r="J12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K12" t="str">
+        <v>4</v>
+      </c>
+      <c r="K12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L12" t="str">
+        <v>4</v>
+      </c>
+      <c r="L12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="str">
+      <c r="A13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B13" t="str">
+        <v>4</v>
+      </c>
+      <c r="B13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D13" t="str">
+        <v>4</v>
+      </c>
+      <c r="D13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E13" t="str">
+        <v>4</v>
+      </c>
+      <c r="E13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+        <v>4</v>
+      </c>
+      <c r="F13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v>4</v>
+      </c>
+      <c r="G13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H13" t="str">
+        <v>4</v>
+      </c>
+      <c r="H13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>4</v>
+      </c>
+      <c r="I13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J13" t="str">
+        <v>4</v>
+      </c>
+      <c r="J13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K13" t="str">
+        <v>4</v>
+      </c>
+      <c r="K13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L13" t="str">
+        <v>4</v>
+      </c>
+      <c r="L13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="str">
+      <c r="A14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B14" t="str">
+        <v>4</v>
+      </c>
+      <c r="B14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C14" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D14" t="str">
+        <v>4</v>
+      </c>
+      <c r="D14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E14" t="str">
+        <v>4</v>
+      </c>
+      <c r="E14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+        <v>4</v>
+      </c>
+      <c r="F14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G14" t="str">
+        <v>4</v>
+      </c>
+      <c r="G14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H14" t="str">
+        <v>4</v>
+      </c>
+      <c r="H14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>4</v>
+      </c>
+      <c r="I14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J14" t="str">
+        <v>4</v>
+      </c>
+      <c r="J14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K14" t="str">
+        <v>4</v>
+      </c>
+      <c r="K14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L14" t="str">
+        <v>4</v>
+      </c>
+      <c r="L14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>4</v>
+      </c>
+      <c r="B15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D15" t="str">
+        <v>4</v>
+      </c>
+      <c r="D15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
+        <v>4</v>
+      </c>
+      <c r="E15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+        <v>4</v>
+      </c>
+      <c r="F15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
+        <v>4</v>
+      </c>
+      <c r="G15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H15" t="str">
+        <v>4</v>
+      </c>
+      <c r="H15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I15" t="str">
+        <v>4</v>
+      </c>
+      <c r="I15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J15" t="str">
+        <v>4</v>
+      </c>
+      <c r="J15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K15" t="str">
+        <v>4</v>
+      </c>
+      <c r="K15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L15" t="str">
+        <v>4</v>
+      </c>
+      <c r="L15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="str">
+      <c r="A16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B16" t="str">
+        <v>4</v>
+      </c>
+      <c r="B16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C16" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D16" t="str">
+        <v>4</v>
+      </c>
+      <c r="D16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
+        <v>4</v>
+      </c>
+      <c r="E16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+        <v>4</v>
+      </c>
+      <c r="F16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>4</v>
+      </c>
+      <c r="G16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H16" t="str">
+        <v>4</v>
+      </c>
+      <c r="H16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v>4</v>
+      </c>
+      <c r="I16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J16" t="str">
+        <v>4</v>
+      </c>
+      <c r="J16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K16" t="str">
+        <v>4</v>
+      </c>
+      <c r="K16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L16" t="str">
+        <v>4</v>
+      </c>
+      <c r="L16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="str">
+      <c r="A17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B17" t="str">
+        <v>4</v>
+      </c>
+      <c r="B17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C17" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D17" t="str">
+        <v>4</v>
+      </c>
+      <c r="D17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>4</v>
+      </c>
+      <c r="E17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+        <v>4</v>
+      </c>
+      <c r="F17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
+        <v>4</v>
+      </c>
+      <c r="G17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H17" t="str">
+        <v>4</v>
+      </c>
+      <c r="H17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I17" t="str">
+        <v>4</v>
+      </c>
+      <c r="I17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J17" t="str">
+        <v>4</v>
+      </c>
+      <c r="J17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K17" t="str">
+        <v>4</v>
+      </c>
+      <c r="K17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L17" t="str">
+        <v>4</v>
+      </c>
+      <c r="L17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="str">
+      <c r="A18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B18" t="str">
+        <v>4</v>
+      </c>
+      <c r="B18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C18" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
+        <v>4</v>
+      </c>
+      <c r="D18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>4</v>
+      </c>
+      <c r="E18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+        <v>4</v>
+      </c>
+      <c r="F18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
+        <v>4</v>
+      </c>
+      <c r="G18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H18" t="str">
+        <v>4</v>
+      </c>
+      <c r="H18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I18" t="str">
+        <v>4</v>
+      </c>
+      <c r="I18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J18" t="str">
+        <v>4</v>
+      </c>
+      <c r="J18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K18" t="str">
+        <v>4</v>
+      </c>
+      <c r="K18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L18" t="str">
+        <v>4</v>
+      </c>
+      <c r="L18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="str">
+      <c r="A19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B19" t="str">
+        <v>4</v>
+      </c>
+      <c r="B19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C19" t="str">
+        <v>4</v>
+      </c>
+      <c r="C19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D19" t="str">
+        <v>4</v>
+      </c>
+      <c r="D19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
+        <v>4</v>
+      </c>
+      <c r="E19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+        <v>4</v>
+      </c>
+      <c r="F19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
+        <v>4</v>
+      </c>
+      <c r="G19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H19" t="str">
+        <v>4</v>
+      </c>
+      <c r="H19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I19" t="str">
+        <v>4</v>
+      </c>
+      <c r="I19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J19" t="str">
+        <v>4</v>
+      </c>
+      <c r="J19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K19" t="str">
+        <v>4</v>
+      </c>
+      <c r="K19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L19" t="str">
+        <v>4</v>
+      </c>
+      <c r="L19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12849,813 +12882,813 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="str">
+      <c r="A2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B2" t="str">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C2" t="str">
+        <v>4</v>
+      </c>
+      <c r="C2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D2" t="str">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E2" t="str">
+        <v>4</v>
+      </c>
+      <c r="E2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F2" t="str">
+        <v>4</v>
+      </c>
+      <c r="F2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G2" t="str">
+        <v>4</v>
+      </c>
+      <c r="G2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H2" t="str">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I2" t="str">
+        <v>4</v>
+      </c>
+      <c r="I2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J2" t="str">
+        <v>4</v>
+      </c>
+      <c r="J2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K2" t="str">
+        <v>4</v>
+      </c>
+      <c r="K2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L2" t="str">
+        <v>4</v>
+      </c>
+      <c r="L2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="str">
+      <c r="A3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B3" t="str">
+        <v>4</v>
+      </c>
+      <c r="B3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C3" t="str">
+        <v>4</v>
+      </c>
+      <c r="C3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D3" t="str">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E3" t="str">
+        <v>4</v>
+      </c>
+      <c r="E3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F3" t="str">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G3" t="str">
+        <v>4</v>
+      </c>
+      <c r="G3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H3" t="str">
+        <v>4</v>
+      </c>
+      <c r="H3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I3" t="str">
+        <v>4</v>
+      </c>
+      <c r="I3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J3" t="str">
+        <v>4</v>
+      </c>
+      <c r="J3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K3" t="str">
+        <v>4</v>
+      </c>
+      <c r="K3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L3" t="str">
+        <v>4</v>
+      </c>
+      <c r="L3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
+      <c r="A4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B4" t="str">
+        <v>4</v>
+      </c>
+      <c r="B4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C4" t="str">
+        <v>4</v>
+      </c>
+      <c r="C4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D4" t="str">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E4" t="str">
+        <v>4</v>
+      </c>
+      <c r="E4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F4" t="str">
+        <v>4</v>
+      </c>
+      <c r="F4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G4" t="str">
+        <v>4</v>
+      </c>
+      <c r="G4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H4" t="str">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I4" t="str">
+        <v>4</v>
+      </c>
+      <c r="I4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J4" t="str">
+        <v>4</v>
+      </c>
+      <c r="J4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K4" t="str">
+        <v>4</v>
+      </c>
+      <c r="K4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L4" t="str">
+        <v>4</v>
+      </c>
+      <c r="L4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C5" t="str">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D5" t="str">
+        <v>4</v>
+      </c>
+      <c r="D5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E5" t="str">
+        <v>4</v>
+      </c>
+      <c r="E5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F5" t="str">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G5" t="str">
+        <v>4</v>
+      </c>
+      <c r="G5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H5" t="str">
+        <v>4</v>
+      </c>
+      <c r="H5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I5" t="str">
+        <v>4</v>
+      </c>
+      <c r="I5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J5" t="str">
+        <v>4</v>
+      </c>
+      <c r="J5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K5" t="str">
+        <v>4</v>
+      </c>
+      <c r="K5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L5" t="str">
+        <v>4</v>
+      </c>
+      <c r="L5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B6" t="str">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C6" t="str">
+        <v>4</v>
+      </c>
+      <c r="C6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D6" t="str">
+        <v>4</v>
+      </c>
+      <c r="D6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E6" t="str">
+        <v>4</v>
+      </c>
+      <c r="E6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F6" t="str">
+        <v>4</v>
+      </c>
+      <c r="F6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G6" t="str">
+        <v>4</v>
+      </c>
+      <c r="G6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H6" t="str">
+        <v>4</v>
+      </c>
+      <c r="H6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I6" t="str">
+        <v>4</v>
+      </c>
+      <c r="I6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J6" t="str">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K6" t="str">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L6" t="str">
+        <v>4</v>
+      </c>
+      <c r="L6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
+      <c r="A7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>4</v>
+      </c>
+      <c r="B7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>4</v>
+      </c>
+      <c r="C7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>4</v>
+      </c>
+      <c r="D7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>4</v>
+      </c>
+      <c r="E7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>4</v>
+      </c>
+      <c r="F7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>4</v>
+      </c>
+      <c r="G7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>4</v>
+      </c>
+      <c r="H7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>4</v>
+      </c>
+      <c r="I7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>4</v>
+      </c>
+      <c r="J7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>4</v>
+      </c>
+      <c r="L7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
+      <c r="A8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B8" t="str">
+        <v>4</v>
+      </c>
+      <c r="B8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C8" t="str">
+        <v>4</v>
+      </c>
+      <c r="C8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D8" t="str">
+        <v>4</v>
+      </c>
+      <c r="D8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E8" t="str">
+        <v>4</v>
+      </c>
+      <c r="E8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+        <v>4</v>
+      </c>
+      <c r="F8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G8" t="str">
+        <v>4</v>
+      </c>
+      <c r="G8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H8" t="str">
+        <v>4</v>
+      </c>
+      <c r="H8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>4</v>
+      </c>
+      <c r="I8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J8" t="str">
+        <v>4</v>
+      </c>
+      <c r="J8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K8" t="str">
+        <v>4</v>
+      </c>
+      <c r="K8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L8" t="str">
+        <v>4</v>
+      </c>
+      <c r="L8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="str">
+      <c r="A9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
+        <v>4</v>
+      </c>
+      <c r="B9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C9" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D9" t="str">
+        <v>4</v>
+      </c>
+      <c r="D9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>4</v>
+      </c>
+      <c r="E9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+        <v>4</v>
+      </c>
+      <c r="F9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G9" t="str">
+        <v>4</v>
+      </c>
+      <c r="G9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H9" t="str">
+        <v>4</v>
+      </c>
+      <c r="H9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>4</v>
+      </c>
+      <c r="I9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J9" t="str">
+        <v>4</v>
+      </c>
+      <c r="J9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K9" t="str">
+        <v>4</v>
+      </c>
+      <c r="K9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L9" t="str">
+        <v>4</v>
+      </c>
+      <c r="L9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="str">
+      <c r="A12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B12" t="str">
+        <v>5</v>
+      </c>
+      <c r="B12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C12" t="str">
+        <v>5</v>
+      </c>
+      <c r="C12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D12" t="str">
+        <v>5</v>
+      </c>
+      <c r="D12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E12" t="str">
+        <v>5</v>
+      </c>
+      <c r="E12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+      <c r="F12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G12" t="str">
+        <v>5</v>
+      </c>
+      <c r="G12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H12" t="str">
+        <v>5</v>
+      </c>
+      <c r="H12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>5</v>
+      </c>
+      <c r="I12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J12" t="str">
+        <v>5</v>
+      </c>
+      <c r="J12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K12" t="str">
+        <v>5</v>
+      </c>
+      <c r="K12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L12" t="str">
+        <v>5</v>
+      </c>
+      <c r="L12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="str">
+      <c r="A13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B13" t="str">
+        <v>5</v>
+      </c>
+      <c r="B13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C13" t="str">
+        <v>5</v>
+      </c>
+      <c r="C13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D13" t="str">
+        <v>5</v>
+      </c>
+      <c r="D13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E13" t="str">
+        <v>5</v>
+      </c>
+      <c r="E13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+      <c r="F13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v>5</v>
+      </c>
+      <c r="G13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H13" t="str">
+        <v>5</v>
+      </c>
+      <c r="H13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>5</v>
+      </c>
+      <c r="I13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J13" t="str">
+        <v>5</v>
+      </c>
+      <c r="J13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K13" t="str">
+        <v>5</v>
+      </c>
+      <c r="K13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L13" t="str">
+        <v>5</v>
+      </c>
+      <c r="L13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="str">
+      <c r="A14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B14" t="str">
+        <v>5</v>
+      </c>
+      <c r="B14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C14" t="str">
+        <v>5</v>
+      </c>
+      <c r="C14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D14" t="str">
+        <v>5</v>
+      </c>
+      <c r="D14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E14" t="str">
+        <v>5</v>
+      </c>
+      <c r="E14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+      <c r="F14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G14" t="str">
+        <v>5</v>
+      </c>
+      <c r="G14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H14" t="str">
+        <v>5</v>
+      </c>
+      <c r="H14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>5</v>
+      </c>
+      <c r="I14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J14" t="str">
+        <v>5</v>
+      </c>
+      <c r="J14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K14" t="str">
+        <v>5</v>
+      </c>
+      <c r="K14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L14" t="str">
+        <v>5</v>
+      </c>
+      <c r="L14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>5</v>
+      </c>
+      <c r="B15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C15" t="str">
+        <v>5</v>
+      </c>
+      <c r="C15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D15" t="str">
+        <v>5</v>
+      </c>
+      <c r="D15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
+        <v>5</v>
+      </c>
+      <c r="E15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+      <c r="F15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
+        <v>5</v>
+      </c>
+      <c r="G15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H15" t="str">
+        <v>5</v>
+      </c>
+      <c r="H15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I15" t="str">
+        <v>5</v>
+      </c>
+      <c r="I15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J15" t="str">
+        <v>5</v>
+      </c>
+      <c r="J15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K15" t="str">
+        <v>5</v>
+      </c>
+      <c r="K15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L15" t="str">
+        <v>5</v>
+      </c>
+      <c r="L15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="str">
+      <c r="A16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B16" t="str">
+        <v>5</v>
+      </c>
+      <c r="B16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C16" t="str">
+        <v>5</v>
+      </c>
+      <c r="C16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D16" t="str">
+        <v>5</v>
+      </c>
+      <c r="D16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
+        <v>5</v>
+      </c>
+      <c r="E16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+      <c r="F16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>5</v>
+      </c>
+      <c r="G16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H16" t="str">
+        <v>5</v>
+      </c>
+      <c r="H16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v>5</v>
+      </c>
+      <c r="I16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J16" t="str">
+        <v>5</v>
+      </c>
+      <c r="J16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K16" t="str">
+        <v>5</v>
+      </c>
+      <c r="K16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L16" t="str">
+        <v>5</v>
+      </c>
+      <c r="L16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="str">
+      <c r="A17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B17" t="str">
+        <v>5</v>
+      </c>
+      <c r="B17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C17" t="str">
+        <v>5</v>
+      </c>
+      <c r="C17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D17" t="str">
+        <v>5</v>
+      </c>
+      <c r="D17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>5</v>
+      </c>
+      <c r="E17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+      <c r="F17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
+        <v>5</v>
+      </c>
+      <c r="G17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H17" t="str">
+        <v>5</v>
+      </c>
+      <c r="H17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I17" t="str">
+        <v>5</v>
+      </c>
+      <c r="I17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J17" t="str">
+        <v>5</v>
+      </c>
+      <c r="J17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K17" t="str">
+        <v>5</v>
+      </c>
+      <c r="K17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L17" t="str">
+        <v>5</v>
+      </c>
+      <c r="L17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="str">
+      <c r="A18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B18" t="str">
+        <v>5</v>
+      </c>
+      <c r="B18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C18" t="str">
+        <v>5</v>
+      </c>
+      <c r="C18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
+        <v>5</v>
+      </c>
+      <c r="D18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>5</v>
+      </c>
+      <c r="E18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+      <c r="F18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
+        <v>5</v>
+      </c>
+      <c r="G18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H18" t="str">
+        <v>5</v>
+      </c>
+      <c r="H18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I18" t="str">
+        <v>5</v>
+      </c>
+      <c r="I18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J18" t="str">
+        <v>5</v>
+      </c>
+      <c r="J18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K18" t="str">
+        <v>5</v>
+      </c>
+      <c r="K18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L18" t="str">
+        <v>5</v>
+      </c>
+      <c r="L18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="str">
+      <c r="A19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B19" t="str">
+        <v>5</v>
+      </c>
+      <c r="B19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C19" t="str">
+        <v>5</v>
+      </c>
+      <c r="C19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D19" t="str">
+        <v>5</v>
+      </c>
+      <c r="D19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
+        <v>5</v>
+      </c>
+      <c r="E19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+      <c r="F19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
+        <v>5</v>
+      </c>
+      <c r="G19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H19" t="str">
+        <v>5</v>
+      </c>
+      <c r="H19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I19" t="str">
+        <v>5</v>
+      </c>
+      <c r="I19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J19" t="str">
+        <v>5</v>
+      </c>
+      <c r="J19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K19" t="str">
+        <v>5</v>
+      </c>
+      <c r="K19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L19" t="str">
+        <v>5</v>
+      </c>
+      <c r="L19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13671,813 +13704,813 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="str">
+      <c r="A2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B2" t="str">
+        <v>5</v>
+      </c>
+      <c r="B2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C2" t="str">
+        <v>5</v>
+      </c>
+      <c r="C2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D2" t="str">
+        <v>5</v>
+      </c>
+      <c r="D2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E2" t="str">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F2" t="str">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G2" t="str">
+        <v>5</v>
+      </c>
+      <c r="G2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H2" t="str">
+        <v>5</v>
+      </c>
+      <c r="H2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I2" t="str">
+        <v>5</v>
+      </c>
+      <c r="I2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J2" t="str">
+        <v>5</v>
+      </c>
+      <c r="J2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K2" t="str">
+        <v>5</v>
+      </c>
+      <c r="K2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L2" t="str">
+        <v>5</v>
+      </c>
+      <c r="L2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="str">
+      <c r="A3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B3" t="str">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C3" t="str">
+        <v>5</v>
+      </c>
+      <c r="C3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D3" t="str">
+        <v>5</v>
+      </c>
+      <c r="D3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E3" t="str">
+        <v>5</v>
+      </c>
+      <c r="E3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F3" t="str">
+        <v>5</v>
+      </c>
+      <c r="F3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G3" t="str">
+        <v>5</v>
+      </c>
+      <c r="G3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H3" t="str">
+        <v>5</v>
+      </c>
+      <c r="H3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I3" t="str">
+        <v>5</v>
+      </c>
+      <c r="I3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J3" t="str">
+        <v>5</v>
+      </c>
+      <c r="J3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K3" t="str">
+        <v>5</v>
+      </c>
+      <c r="K3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L3" t="str">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
+      <c r="A4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B4" t="str">
+        <v>5</v>
+      </c>
+      <c r="B4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C4" t="str">
+        <v>5</v>
+      </c>
+      <c r="C4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D4" t="str">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E4" t="str">
+        <v>5</v>
+      </c>
+      <c r="E4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F4" t="str">
+        <v>5</v>
+      </c>
+      <c r="F4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G4" t="str">
+        <v>5</v>
+      </c>
+      <c r="G4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H4" t="str">
+        <v>5</v>
+      </c>
+      <c r="H4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I4" t="str">
+        <v>5</v>
+      </c>
+      <c r="I4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J4" t="str">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K4" t="str">
+        <v>5</v>
+      </c>
+      <c r="K4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L4" t="str">
+        <v>5</v>
+      </c>
+      <c r="L4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B5" t="str">
+        <v>5</v>
+      </c>
+      <c r="B5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C5" t="str">
+        <v>5</v>
+      </c>
+      <c r="C5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D5" t="str">
+        <v>5</v>
+      </c>
+      <c r="D5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E5" t="str">
+        <v>5</v>
+      </c>
+      <c r="E5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F5" t="str">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G5" t="str">
+        <v>5</v>
+      </c>
+      <c r="G5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H5" t="str">
+        <v>5</v>
+      </c>
+      <c r="H5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I5" t="str">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J5" t="str">
+        <v>5</v>
+      </c>
+      <c r="J5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K5" t="str">
+        <v>5</v>
+      </c>
+      <c r="K5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L5" t="str">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C6" t="str">
+        <v>5</v>
+      </c>
+      <c r="C6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D6" t="str">
+        <v>5</v>
+      </c>
+      <c r="D6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F6" t="str">
+        <v>5</v>
+      </c>
+      <c r="F6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G6" t="str">
+        <v>5</v>
+      </c>
+      <c r="G6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H6" t="str">
+        <v>5</v>
+      </c>
+      <c r="H6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I6" t="str">
+        <v>5</v>
+      </c>
+      <c r="I6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J6" t="str">
+        <v>5</v>
+      </c>
+      <c r="J6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K6" t="str">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L6" t="str">
+        <v>5</v>
+      </c>
+      <c r="L6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
+      <c r="A7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>5</v>
+      </c>
+      <c r="B7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>5</v>
+      </c>
+      <c r="D7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>5</v>
+      </c>
+      <c r="E7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>5</v>
+      </c>
+      <c r="F7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>5</v>
+      </c>
+      <c r="G7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>5</v>
+      </c>
+      <c r="H7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>5</v>
+      </c>
+      <c r="I7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>5</v>
+      </c>
+      <c r="J7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>5</v>
+      </c>
+      <c r="L7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
+      <c r="A8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B8" t="str">
+        <v>5</v>
+      </c>
+      <c r="B8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C8" t="str">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D8" t="str">
+        <v>5</v>
+      </c>
+      <c r="D8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E8" t="str">
+        <v>5</v>
+      </c>
+      <c r="E8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+        <v>5</v>
+      </c>
+      <c r="F8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G8" t="str">
+        <v>5</v>
+      </c>
+      <c r="G8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H8" t="str">
+        <v>5</v>
+      </c>
+      <c r="H8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>5</v>
+      </c>
+      <c r="I8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J8" t="str">
+        <v>5</v>
+      </c>
+      <c r="J8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K8" t="str">
+        <v>5</v>
+      </c>
+      <c r="K8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L8" t="str">
+        <v>5</v>
+      </c>
+      <c r="L8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="str">
+      <c r="A9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
+        <v>5</v>
+      </c>
+      <c r="B9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C9" t="str">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D9" t="str">
+        <v>5</v>
+      </c>
+      <c r="D9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>5</v>
+      </c>
+      <c r="E9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+        <v>5</v>
+      </c>
+      <c r="F9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G9" t="str">
+        <v>5</v>
+      </c>
+      <c r="G9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H9" t="str">
+        <v>5</v>
+      </c>
+      <c r="H9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>5</v>
+      </c>
+      <c r="I9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J9" t="str">
+        <v>5</v>
+      </c>
+      <c r="J9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K9" t="str">
+        <v>5</v>
+      </c>
+      <c r="K9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L9" t="str">
+        <v>5</v>
+      </c>
+      <c r="L9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="str">
+      <c r="A12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B12" t="str">
+        <v>6</v>
+      </c>
+      <c r="B12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C12" t="str">
+        <v>6</v>
+      </c>
+      <c r="C12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D12" t="str">
+        <v>6</v>
+      </c>
+      <c r="D12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E12" t="str">
+        <v>6</v>
+      </c>
+      <c r="E12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+        <v>6</v>
+      </c>
+      <c r="F12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G12" t="str">
+        <v>6</v>
+      </c>
+      <c r="G12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H12" t="str">
+        <v>6</v>
+      </c>
+      <c r="H12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>6</v>
+      </c>
+      <c r="I12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J12" t="str">
+        <v>6</v>
+      </c>
+      <c r="J12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K12" t="str">
+        <v>6</v>
+      </c>
+      <c r="K12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L12" t="str">
+        <v>6</v>
+      </c>
+      <c r="L12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="str">
+      <c r="A13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B13" t="str">
+        <v>6</v>
+      </c>
+      <c r="B13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C13" t="str">
+        <v>6</v>
+      </c>
+      <c r="C13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D13" t="str">
+        <v>6</v>
+      </c>
+      <c r="D13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E13" t="str">
+        <v>6</v>
+      </c>
+      <c r="E13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+        <v>6</v>
+      </c>
+      <c r="F13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v>6</v>
+      </c>
+      <c r="G13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H13" t="str">
+        <v>6</v>
+      </c>
+      <c r="H13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>6</v>
+      </c>
+      <c r="I13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J13" t="str">
+        <v>6</v>
+      </c>
+      <c r="J13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K13" t="str">
+        <v>6</v>
+      </c>
+      <c r="K13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L13" t="str">
+        <v>6</v>
+      </c>
+      <c r="L13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="str">
+      <c r="A14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B14" t="str">
+        <v>6</v>
+      </c>
+      <c r="B14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C14" t="str">
+        <v>6</v>
+      </c>
+      <c r="C14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D14" t="str">
+        <v>6</v>
+      </c>
+      <c r="D14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E14" t="str">
+        <v>6</v>
+      </c>
+      <c r="E14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+        <v>6</v>
+      </c>
+      <c r="F14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G14" t="str">
+        <v>6</v>
+      </c>
+      <c r="G14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H14" t="str">
+        <v>6</v>
+      </c>
+      <c r="H14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>6</v>
+      </c>
+      <c r="I14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J14" t="str">
+        <v>6</v>
+      </c>
+      <c r="J14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K14" t="str">
+        <v>6</v>
+      </c>
+      <c r="K14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L14" t="str">
+        <v>6</v>
+      </c>
+      <c r="L14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>6</v>
+      </c>
+      <c r="B15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C15" t="str">
+        <v>6</v>
+      </c>
+      <c r="C15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D15" t="str">
+        <v>6</v>
+      </c>
+      <c r="D15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
+        <v>6</v>
+      </c>
+      <c r="E15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+        <v>6</v>
+      </c>
+      <c r="F15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
+        <v>6</v>
+      </c>
+      <c r="G15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H15" t="str">
+        <v>6</v>
+      </c>
+      <c r="H15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I15" t="str">
+        <v>6</v>
+      </c>
+      <c r="I15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J15" t="str">
+        <v>6</v>
+      </c>
+      <c r="J15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K15" t="str">
+        <v>6</v>
+      </c>
+      <c r="K15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L15" t="str">
+        <v>6</v>
+      </c>
+      <c r="L15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="str">
+      <c r="A16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B16" t="str">
+        <v>6</v>
+      </c>
+      <c r="B16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C16" t="str">
+        <v>6</v>
+      </c>
+      <c r="C16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D16" t="str">
+        <v>6</v>
+      </c>
+      <c r="D16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
+        <v>6</v>
+      </c>
+      <c r="E16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+        <v>6</v>
+      </c>
+      <c r="F16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>6</v>
+      </c>
+      <c r="G16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H16" t="str">
+        <v>6</v>
+      </c>
+      <c r="H16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v>6</v>
+      </c>
+      <c r="I16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J16" t="str">
+        <v>6</v>
+      </c>
+      <c r="J16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K16" t="str">
+        <v>6</v>
+      </c>
+      <c r="K16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L16" t="str">
+        <v>6</v>
+      </c>
+      <c r="L16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="str">
+      <c r="A17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B17" t="str">
+        <v>6</v>
+      </c>
+      <c r="B17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C17" t="str">
+        <v>6</v>
+      </c>
+      <c r="C17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D17" t="str">
+        <v>6</v>
+      </c>
+      <c r="D17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>6</v>
+      </c>
+      <c r="E17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+        <v>6</v>
+      </c>
+      <c r="F17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
+        <v>6</v>
+      </c>
+      <c r="G17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H17" t="str">
+        <v>6</v>
+      </c>
+      <c r="H17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I17" t="str">
+        <v>6</v>
+      </c>
+      <c r="I17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J17" t="str">
+        <v>6</v>
+      </c>
+      <c r="J17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K17" t="str">
+        <v>6</v>
+      </c>
+      <c r="K17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L17" t="str">
+        <v>6</v>
+      </c>
+      <c r="L17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="str">
+      <c r="A18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B18" t="str">
+        <v>6</v>
+      </c>
+      <c r="B18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C18" t="str">
+        <v>6</v>
+      </c>
+      <c r="C18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
+        <v>6</v>
+      </c>
+      <c r="D18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>6</v>
+      </c>
+      <c r="E18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+        <v>6</v>
+      </c>
+      <c r="F18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
+        <v>6</v>
+      </c>
+      <c r="G18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H18" t="str">
+        <v>6</v>
+      </c>
+      <c r="H18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I18" t="str">
+        <v>6</v>
+      </c>
+      <c r="I18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J18" t="str">
+        <v>6</v>
+      </c>
+      <c r="J18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K18" t="str">
+        <v>6</v>
+      </c>
+      <c r="K18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L18" t="str">
+        <v>6</v>
+      </c>
+      <c r="L18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="str">
+      <c r="A19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B19" t="str">
+        <v>6</v>
+      </c>
+      <c r="B19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C19" t="str">
+        <v>6</v>
+      </c>
+      <c r="C19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D19" t="str">
+        <v>6</v>
+      </c>
+      <c r="D19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
+        <v>6</v>
+      </c>
+      <c r="E19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+        <v>6</v>
+      </c>
+      <c r="F19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
+        <v>6</v>
+      </c>
+      <c r="G19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H19" t="str">
+        <v>6</v>
+      </c>
+      <c r="H19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I19" t="str">
+        <v>6</v>
+      </c>
+      <c r="I19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J19" t="str">
+        <v>6</v>
+      </c>
+      <c r="J19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K19" t="str">
+        <v>6</v>
+      </c>
+      <c r="K19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L19" t="str">
+        <v>6</v>
+      </c>
+      <c r="L19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -14493,813 +14526,813 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="str">
+      <c r="A2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B2" t="str">
+        <v>6</v>
+      </c>
+      <c r="B2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C2" t="str">
+        <v>6</v>
+      </c>
+      <c r="C2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D2" t="str">
+        <v>6</v>
+      </c>
+      <c r="D2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E2" t="str">
+        <v>6</v>
+      </c>
+      <c r="E2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F2" t="str">
+        <v>6</v>
+      </c>
+      <c r="F2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G2" t="str">
+        <v>6</v>
+      </c>
+      <c r="G2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H2" t="str">
+        <v>6</v>
+      </c>
+      <c r="H2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I2" t="str">
+        <v>6</v>
+      </c>
+      <c r="I2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J2" t="str">
+        <v>6</v>
+      </c>
+      <c r="J2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K2" t="str">
+        <v>6</v>
+      </c>
+      <c r="K2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L2" t="str">
+        <v>6</v>
+      </c>
+      <c r="L2">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="str">
+      <c r="A3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B3" t="str">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C3" t="str">
+        <v>6</v>
+      </c>
+      <c r="C3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D3" t="str">
+        <v>6</v>
+      </c>
+      <c r="D3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E3" t="str">
+        <v>6</v>
+      </c>
+      <c r="E3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F3" t="str">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G3" t="str">
+        <v>6</v>
+      </c>
+      <c r="G3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H3" t="str">
+        <v>6</v>
+      </c>
+      <c r="H3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I3" t="str">
+        <v>6</v>
+      </c>
+      <c r="I3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J3" t="str">
+        <v>6</v>
+      </c>
+      <c r="J3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K3" t="str">
+        <v>6</v>
+      </c>
+      <c r="K3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L3" t="str">
+        <v>6</v>
+      </c>
+      <c r="L3">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
+      <c r="A4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B4" t="str">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C4" t="str">
+        <v>6</v>
+      </c>
+      <c r="C4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D4" t="str">
+        <v>6</v>
+      </c>
+      <c r="D4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E4" t="str">
+        <v>6</v>
+      </c>
+      <c r="E4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F4" t="str">
+        <v>6</v>
+      </c>
+      <c r="F4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G4" t="str">
+        <v>6</v>
+      </c>
+      <c r="G4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H4" t="str">
+        <v>6</v>
+      </c>
+      <c r="H4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I4" t="str">
+        <v>6</v>
+      </c>
+      <c r="I4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J4" t="str">
+        <v>6</v>
+      </c>
+      <c r="J4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K4" t="str">
+        <v>6</v>
+      </c>
+      <c r="K4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L4" t="str">
+        <v>6</v>
+      </c>
+      <c r="L4">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B5" t="str">
+        <v>6</v>
+      </c>
+      <c r="B5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C5" t="str">
+        <v>6</v>
+      </c>
+      <c r="C5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D5" t="str">
+        <v>6</v>
+      </c>
+      <c r="D5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E5" t="str">
+        <v>6</v>
+      </c>
+      <c r="E5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F5" t="str">
+        <v>6</v>
+      </c>
+      <c r="F5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G5" t="str">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H5" t="str">
+        <v>6</v>
+      </c>
+      <c r="H5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I5" t="str">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J5" t="str">
+        <v>6</v>
+      </c>
+      <c r="J5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K5" t="str">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L5" t="str">
+        <v>6</v>
+      </c>
+      <c r="L5">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B6" t="str">
+        <v>6</v>
+      </c>
+      <c r="B6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C6" t="str">
+        <v>6</v>
+      </c>
+      <c r="C6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D6" t="str">
+        <v>6</v>
+      </c>
+      <c r="D6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E6" t="str">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F6" t="str">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G6" t="str">
+        <v>6</v>
+      </c>
+      <c r="G6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H6" t="str">
+        <v>6</v>
+      </c>
+      <c r="H6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I6" t="str">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J6" t="str">
+        <v>6</v>
+      </c>
+      <c r="J6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K6" t="str">
+        <v>6</v>
+      </c>
+      <c r="K6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L6" t="str">
+        <v>6</v>
+      </c>
+      <c r="L6">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
+      <c r="A7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>6</v>
+      </c>
+      <c r="B7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>6</v>
+      </c>
+      <c r="C7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>6</v>
+      </c>
+      <c r="D7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>6</v>
+      </c>
+      <c r="E7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>6</v>
+      </c>
+      <c r="F7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>6</v>
+      </c>
+      <c r="G7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>6</v>
+      </c>
+      <c r="H7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>6</v>
+      </c>
+      <c r="I7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>6</v>
+      </c>
+      <c r="J7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>6</v>
+      </c>
+      <c r="K7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>6</v>
+      </c>
+      <c r="L7">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
+      <c r="A8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B8" t="str">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C8" t="str">
+        <v>6</v>
+      </c>
+      <c r="C8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D8" t="str">
+        <v>6</v>
+      </c>
+      <c r="D8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E8" t="str">
+        <v>6</v>
+      </c>
+      <c r="E8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+        <v>6</v>
+      </c>
+      <c r="F8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G8" t="str">
+        <v>6</v>
+      </c>
+      <c r="G8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H8" t="str">
+        <v>6</v>
+      </c>
+      <c r="H8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>6</v>
+      </c>
+      <c r="I8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J8" t="str">
+        <v>6</v>
+      </c>
+      <c r="J8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K8" t="str">
+        <v>6</v>
+      </c>
+      <c r="K8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L8" t="str">
+        <v>6</v>
+      </c>
+      <c r="L8">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="str">
+      <c r="A9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
+        <v>6</v>
+      </c>
+      <c r="B9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C9" t="str">
+        <v>6</v>
+      </c>
+      <c r="C9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D9" t="str">
+        <v>6</v>
+      </c>
+      <c r="D9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>6</v>
+      </c>
+      <c r="E9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+        <v>6</v>
+      </c>
+      <c r="F9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G9" t="str">
+        <v>6</v>
+      </c>
+      <c r="G9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H9" t="str">
+        <v>6</v>
+      </c>
+      <c r="H9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>6</v>
+      </c>
+      <c r="I9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J9" t="str">
+        <v>6</v>
+      </c>
+      <c r="J9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K9" t="str">
+        <v>6</v>
+      </c>
+      <c r="K9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L9" t="str">
+        <v>6</v>
+      </c>
+      <c r="L9">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="str">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="str">
+      <c r="A12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B12" t="str">
+        <v>7</v>
+      </c>
+      <c r="B12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C12" t="str">
+        <v>7</v>
+      </c>
+      <c r="C12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D12" t="str">
+        <v>7</v>
+      </c>
+      <c r="D12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E12" t="str">
+        <v>7</v>
+      </c>
+      <c r="E12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+        <v>7</v>
+      </c>
+      <c r="F12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G12" t="str">
+        <v>7</v>
+      </c>
+      <c r="G12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H12" t="str">
+        <v>7</v>
+      </c>
+      <c r="H12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>7</v>
+      </c>
+      <c r="I12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J12" t="str">
+        <v>7</v>
+      </c>
+      <c r="J12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K12" t="str">
+        <v>7</v>
+      </c>
+      <c r="K12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L12" t="str">
+        <v>7</v>
+      </c>
+      <c r="L12">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="str">
+      <c r="A13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B13" t="str">
+        <v>7</v>
+      </c>
+      <c r="B13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C13" t="str">
+        <v>7</v>
+      </c>
+      <c r="C13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D13" t="str">
+        <v>7</v>
+      </c>
+      <c r="D13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E13" t="str">
+        <v>7</v>
+      </c>
+      <c r="E13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+        <v>7</v>
+      </c>
+      <c r="F13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v>7</v>
+      </c>
+      <c r="G13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H13" t="str">
+        <v>7</v>
+      </c>
+      <c r="H13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>7</v>
+      </c>
+      <c r="I13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J13" t="str">
+        <v>7</v>
+      </c>
+      <c r="J13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K13" t="str">
+        <v>7</v>
+      </c>
+      <c r="K13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L13" t="str">
+        <v>7</v>
+      </c>
+      <c r="L13">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="str">
+      <c r="A14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B14" t="str">
+        <v>7</v>
+      </c>
+      <c r="B14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C14" t="str">
+        <v>7</v>
+      </c>
+      <c r="C14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D14" t="str">
+        <v>7</v>
+      </c>
+      <c r="D14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E14" t="str">
+        <v>7</v>
+      </c>
+      <c r="E14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+        <v>7</v>
+      </c>
+      <c r="F14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G14" t="str">
+        <v>7</v>
+      </c>
+      <c r="G14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H14" t="str">
+        <v>7</v>
+      </c>
+      <c r="H14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>7</v>
+      </c>
+      <c r="I14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J14" t="str">
+        <v>7</v>
+      </c>
+      <c r="J14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K14" t="str">
+        <v>7</v>
+      </c>
+      <c r="K14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L14" t="str">
+        <v>7</v>
+      </c>
+      <c r="L14">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>7</v>
+      </c>
+      <c r="B15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C15" t="str">
+        <v>7</v>
+      </c>
+      <c r="C15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D15" t="str">
+        <v>7</v>
+      </c>
+      <c r="D15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
+        <v>7</v>
+      </c>
+      <c r="E15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+        <v>7</v>
+      </c>
+      <c r="F15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
+        <v>7</v>
+      </c>
+      <c r="G15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H15" t="str">
+        <v>7</v>
+      </c>
+      <c r="H15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I15" t="str">
+        <v>7</v>
+      </c>
+      <c r="I15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J15" t="str">
+        <v>7</v>
+      </c>
+      <c r="J15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K15" t="str">
+        <v>7</v>
+      </c>
+      <c r="K15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L15" t="str">
+        <v>7</v>
+      </c>
+      <c r="L15">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="str">
+      <c r="A16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B16" t="str">
+        <v>7</v>
+      </c>
+      <c r="B16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C16" t="str">
+        <v>7</v>
+      </c>
+      <c r="C16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D16" t="str">
+        <v>7</v>
+      </c>
+      <c r="D16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
+        <v>7</v>
+      </c>
+      <c r="E16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+        <v>7</v>
+      </c>
+      <c r="F16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>7</v>
+      </c>
+      <c r="G16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H16" t="str">
+        <v>7</v>
+      </c>
+      <c r="H16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v>7</v>
+      </c>
+      <c r="I16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J16" t="str">
+        <v>7</v>
+      </c>
+      <c r="J16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K16" t="str">
+        <v>7</v>
+      </c>
+      <c r="K16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L16" t="str">
+        <v>7</v>
+      </c>
+      <c r="L16">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="str">
+      <c r="A17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B17" t="str">
+        <v>7</v>
+      </c>
+      <c r="B17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C17" t="str">
+        <v>7</v>
+      </c>
+      <c r="C17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D17" t="str">
+        <v>7</v>
+      </c>
+      <c r="D17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>7</v>
+      </c>
+      <c r="E17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+        <v>7</v>
+      </c>
+      <c r="F17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
+        <v>7</v>
+      </c>
+      <c r="G17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H17" t="str">
+        <v>7</v>
+      </c>
+      <c r="H17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I17" t="str">
+        <v>7</v>
+      </c>
+      <c r="I17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J17" t="str">
+        <v>7</v>
+      </c>
+      <c r="J17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K17" t="str">
+        <v>7</v>
+      </c>
+      <c r="K17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L17" t="str">
+        <v>7</v>
+      </c>
+      <c r="L17">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="str">
+      <c r="A18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B18" t="str">
+        <v>7</v>
+      </c>
+      <c r="B18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C18" t="str">
+        <v>7</v>
+      </c>
+      <c r="C18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
+        <v>7</v>
+      </c>
+      <c r="D18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>7</v>
+      </c>
+      <c r="E18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+        <v>7</v>
+      </c>
+      <c r="F18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
+        <v>7</v>
+      </c>
+      <c r="G18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H18" t="str">
+        <v>7</v>
+      </c>
+      <c r="H18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I18" t="str">
+        <v>7</v>
+      </c>
+      <c r="I18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J18" t="str">
+        <v>7</v>
+      </c>
+      <c r="J18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K18" t="str">
+        <v>7</v>
+      </c>
+      <c r="K18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L18" t="str">
+        <v>7</v>
+      </c>
+      <c r="L18">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="str">
+      <c r="A19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B19" t="str">
+        <v>7</v>
+      </c>
+      <c r="B19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C19" t="str">
+        <v>7</v>
+      </c>
+      <c r="C19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D19" t="str">
+        <v>7</v>
+      </c>
+      <c r="D19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
+        <v>7</v>
+      </c>
+      <c r="E19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+        <v>7</v>
+      </c>
+      <c r="F19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
+        <v>7</v>
+      </c>
+      <c r="G19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H19" t="str">
+        <v>7</v>
+      </c>
+      <c r="H19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I19" t="str">
+        <v>7</v>
+      </c>
+      <c r="I19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J19" t="str">
+        <v>7</v>
+      </c>
+      <c r="J19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K19" t="str">
+        <v>7</v>
+      </c>
+      <c r="K19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L19" t="str">
+        <v>7</v>
+      </c>
+      <c r="L19">
         <f>IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/bio_workcell/active_runs/Sample Excel Experiment Run Document.xlsx
+++ b/bio_workcell/active_runs/Sample Excel Experiment Run Document.xlsx
@@ -182,7 +182,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.13"/>
@@ -193,13 +193,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -210,25 +210,25 @@
         <f aca="false">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="str">
+      <c r="C3" s="2" t="n">
         <f aca="false">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
-        <v/>
-      </c>
-      <c r="D3" s="1" t="str">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <f aca="false">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
-        <v/>
-      </c>
-      <c r="E3" s="1" t="str">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <f aca="false">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
-        <v/>
-      </c>
-      <c r="F3" s="1" t="str">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <f aca="false">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="str">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <f aca="false">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="str">
         <f aca="false">IF((COLUMN() -1) &lt;= $B$1, COLUMN() - 1, "")</f>
@@ -262,11 +262,21 @@
       <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -282,11 +292,21 @@
       <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="C5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -330,7 +350,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
@@ -1161,7 +1181,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
@@ -1992,7 +2012,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
@@ -2823,7 +2843,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
@@ -3654,7 +3674,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
@@ -4485,7 +4505,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:ZZ9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.06"/>
   </cols>
@@ -4553,23 +4573,23 @@
       </c>
       <c r="B8" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="C8" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="D8" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="F8" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="G8" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
@@ -7363,23 +7383,23 @@
       </c>
       <c r="B9" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="C9" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="D9" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="F9" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
-        <v/>
+        <v>Dropdown</v>
       </c>
       <c r="G9" s="0" t="str">
         <f aca="false">IF(COLUMN() &lt;= Complete_Run_Layout!$B$1, "Dropdown", "")</f>
@@ -10183,7 +10203,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
@@ -11014,818 +11034,818 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="str">
+      <c r="A2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L2" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="str">
+      <c r="A3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L3" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="str">
+      <c r="A4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="str">
+      <c r="A5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="str">
+      <c r="A6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L6" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="str">
+      <c r="A7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L7" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="str">
+      <c r="A8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L8" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="str">
+      <c r="A9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="B9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="E9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="I9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
-      </c>
-      <c r="L9" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$4)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="str">
+      <c r="A12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L12" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
+      <c r="A13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L13" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="str">
+      <c r="A14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L14" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="str">
+      <c r="A15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L15" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="str">
+      <c r="A16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L16" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="str">
+      <c r="A17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L17" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="str">
+      <c r="A18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L18" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="str">
+      <c r="A19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="B19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="B19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="C19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="D19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="D19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="E19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="F19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="G19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="G19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="H19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="H19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="I19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="I19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="J19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="J19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="K19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
-      </c>
-      <c r="L19" s="0" t="str">
+        <v>2</v>
+      </c>
+      <c r="L19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$C$4),ISBLANK(Complete_Run_Layout!$C$5),ISBLANK(Complete_Run_Layout!$C$3), Complete_Run_Layout!$C$3 = ""), "", Complete_Run_Layout!$C$5)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -11845,818 +11865,818 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="str">
+      <c r="A2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L2" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="str">
+      <c r="A3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L3" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="str">
+      <c r="A4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="str">
+      <c r="A5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="str">
+      <c r="A6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L6" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="str">
+      <c r="A7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L7" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="str">
+      <c r="A8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="str">
+      <c r="A9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="B9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="C9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="E9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="F9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="G9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="H9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="I9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="J9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="K9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
-      </c>
-      <c r="L9" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$4)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="str">
+      <c r="A12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L12" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
+      <c r="A13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L13" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="str">
+      <c r="A14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L14" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="str">
+      <c r="A15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L15" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="str">
+      <c r="A16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L16" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="str">
+      <c r="A17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L17" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="str">
+      <c r="A18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L18" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="str">
+      <c r="A19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="B19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="B19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="C19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="C19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="D19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="F19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="G19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="H19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="H19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="I19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="I19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="J19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="J19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="K19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
-      </c>
-      <c r="L19" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="L19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$D$4),ISBLANK(Complete_Run_Layout!$D$5),ISBLANK(Complete_Run_Layout!$D$3), Complete_Run_Layout!$D$3 = ""), "", Complete_Run_Layout!$D$5)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12676,818 +12696,818 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="str">
+      <c r="A2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="str">
+      <c r="A3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L3" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="str">
+      <c r="A4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="str">
+      <c r="A5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="str">
+      <c r="A6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L6" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="str">
+      <c r="A7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L7" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="str">
+      <c r="A8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L8" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="str">
+      <c r="A9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="B9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="C9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="D9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="E9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="F9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="G9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="H9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="I9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="J9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="K9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
-      </c>
-      <c r="L9" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$4)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="str">
+      <c r="A12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L12" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
+      <c r="A13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L13" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="str">
+      <c r="A14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L14" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="str">
+      <c r="A15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L15" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="str">
+      <c r="A16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L16" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="str">
+      <c r="A17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L17" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="str">
+      <c r="A18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L18" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="str">
+      <c r="A19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="B19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="C19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="C19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="D19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="E19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="F19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="F19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="G19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="H19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="I19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="J19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="K19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
-      </c>
-      <c r="L19" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="L19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$E$4),ISBLANK(Complete_Run_Layout!$E$5),ISBLANK(Complete_Run_Layout!$E$3), Complete_Run_Layout!$E$3 = ""), "", Complete_Run_Layout!$E$5)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13507,818 +13527,818 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="str">
+      <c r="A2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L2" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="str">
+      <c r="A3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="str">
+      <c r="A4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="str">
+      <c r="A5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="str">
+      <c r="A6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="str">
+      <c r="A7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L7" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="str">
+      <c r="A8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L8" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="str">
+      <c r="A9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="B9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="C9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="D9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="E9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="F9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="G9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="H9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="I9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="J9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="K9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
-      </c>
-      <c r="L9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$4)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="str">
+      <c r="A12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L12" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
+      <c r="A13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L13" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="str">
+      <c r="A14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L14" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="str">
+      <c r="A15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L15" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="str">
+      <c r="A16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L16" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="str">
+      <c r="A17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L17" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="str">
+      <c r="A18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L18" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="str">
+      <c r="A19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="B19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="C19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="C19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="D19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="E19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="F19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="F19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="G19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="G19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="H19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="H19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="I19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="I19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="J19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="J19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="K19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
-      </c>
-      <c r="L19" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="L19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$F$4),ISBLANK(Complete_Run_Layout!$F$5),ISBLANK(Complete_Run_Layout!$F$3), Complete_Run_Layout!$F$3 = ""), "", Complete_Run_Layout!$F$5)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14338,818 +14358,818 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "","MEDIA CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>MEDIA CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="str">
+      <c r="A2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L2" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L2" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="str">
+      <c r="A3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L3" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L3" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="str">
+      <c r="A4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L4" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="str">
+      <c r="A5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L5" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="str">
+      <c r="A6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L6" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="str">
+      <c r="A7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L7" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="str">
+      <c r="A8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L8" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L8" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="str">
+      <c r="A9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="B9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="C9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="D9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="E9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="F9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="G9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="H9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="I9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="J9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="K9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
-      </c>
-      <c r="L9" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L9" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$4)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "","CULTURE CONFIGURATION - 96 WELL")</f>
-        <v/>
+        <v>CULTURE CONFIGURATION - 96 WELL</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="str">
+      <c r="A12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L12" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L12" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
+      <c r="A13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L13" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="str">
+      <c r="A14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L14" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="str">
+      <c r="A15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L15" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L15" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="str">
+      <c r="A16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L16" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="str">
+      <c r="A17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L17" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="str">
+      <c r="A18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L18" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L18" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="str">
+      <c r="A19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="B19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="C19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="C19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="D19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="D19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="E19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="F19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="F19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="G19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="G19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="H19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="H19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="I19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="I19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="J19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="J19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="K19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
-      </c>
-      <c r="L19" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="L19" s="0" t="n">
         <f aca="false">IF(OR(ISBLANK(Complete_Run_Layout!$G$4),ISBLANK(Complete_Run_Layout!$G$5),ISBLANK(Complete_Run_Layout!$G$3), Complete_Run_Layout!$G$3 = ""), "", Complete_Run_Layout!$G$5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -15169,7 +15189,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
